--- a/data/IN.xlsx
+++ b/data/IN.xlsx
@@ -1,16 +1,16 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
 <workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr6="http://schemas.microsoft.com/office/spreadsheetml/2016/revision6" xmlns:xr10="http://schemas.microsoft.com/office/spreadsheetml/2016/revision10" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" mc:Ignorable="x15 xr xr6 xr10 xr2">
-  <fileVersion appName="xl" lastEdited="7" lowestEdited="7" rupBuild="24334"/>
+  <fileVersion appName="xl" lastEdited="7" lowestEdited="7" rupBuild="30326"/>
   <workbookPr defaultThemeVersion="166925"/>
   <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
     <mc:Choice Requires="x15">
-      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="D:\2025-27 PGDM 2nd Year\Ravinder sir\2025-27 TERM 5\Attendance sheet of term-5\"/>
+      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\Sritam\Downloads\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{5501725C-C425-4603-85BF-F9EDD7BB9B8D}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{99825B73-05E8-4854-9A5C-EDB0DADB7D52}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="-120" yWindow="-120" windowWidth="20730" windowHeight="11040" activeTab="2" xr2:uid="{4E5C73C9-1AF8-4C00-BE4F-E60224422A7C}"/>
+    <workbookView xWindow="-110" yWindow="-110" windowWidth="19420" windowHeight="11500" xr2:uid="{4E5C73C9-1AF8-4C00-BE4F-E60224422A7C}"/>
   </bookViews>
   <sheets>
     <sheet name="A" sheetId="1" r:id="rId1"/>
@@ -36,15 +36,12 @@
         <xcalcf:feature name="microsoft.com:LET_WF"/>
       </xcalcf:calcFeatures>
     </ext>
-    <ext xmlns:xlwcv="http://schemas.microsoft.com/office/spreadsheetml/2024/workbookCompatibilityVersion" uri="{D14903EA-33C4-47F7-8F05-3474C54BE107}">
-      <xlwcv:version setVersion="1"/>
-    </ext>
   </extLst>
 </workbook>
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="587" uniqueCount="294">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="589" uniqueCount="296">
   <si>
     <t>Roll No</t>
   </si>
@@ -926,13 +923,19 @@
   </si>
   <si>
     <t>pgdm25chaitanya_s@mdi.ac.in</t>
+  </si>
+  <si>
+    <t>25P055</t>
+  </si>
+  <si>
+    <t>Sritam Tripathy</t>
   </si>
 </sst>
 </file>
 
 <file path=xl/styles.xml><?xml version="1.0" encoding="utf-8"?>
 <styleSheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:x16r2="http://schemas.microsoft.com/office/spreadsheetml/2015/02/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" mc:Ignorable="x14ac x16r2 xr">
-  <fonts count="3" x14ac:knownFonts="1">
+  <fonts count="4" x14ac:knownFonts="1">
     <font>
       <sz val="11"/>
       <color theme="1"/>
@@ -951,6 +954,12 @@
       <u/>
       <sz val="11"/>
       <color theme="10"/>
+      <name val="Calibri"/>
+      <family val="2"/>
+      <scheme val="minor"/>
+    </font>
+    <font>
+      <sz val="8"/>
       <name val="Calibri"/>
       <family val="2"/>
       <scheme val="minor"/>
@@ -1014,7 +1023,7 @@
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyAlignment="1">
       <alignment horizontal="center"/>
     </xf>
-    <xf numFmtId="0" fontId="1" fillId="0" borderId="2" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="1" fillId="0" borderId="2" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" wrapText="1"/>
     </xf>
     <xf numFmtId="0" fontId="2" fillId="0" borderId="1" xfId="1" applyBorder="1" applyAlignment="1">
@@ -1436,14 +1445,14 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{44AB4FCD-9C43-4E11-BD25-F421A4C89615}">
-  <dimension ref="A1:C34"/>
-  <sheetFormatPr defaultRowHeight="15" x14ac:dyDescent="0.25"/>
+  <dimension ref="A1:C35"/>
+  <sheetFormatPr defaultRowHeight="14.5" x14ac:dyDescent="0.35"/>
   <cols>
     <col min="1" max="2" width="10" customWidth="1"/>
-    <col min="3" max="3" width="18.42578125" customWidth="1"/>
+    <col min="3" max="3" width="18.453125" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:3" x14ac:dyDescent="0.25">
+    <row r="1" spans="1:3" x14ac:dyDescent="0.35">
       <c r="A1" s="1" t="s">
         <v>172</v>
       </c>
@@ -1454,7 +1463,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="2" spans="1:3" x14ac:dyDescent="0.25">
+    <row r="2" spans="1:3" x14ac:dyDescent="0.35">
       <c r="A2" s="1">
         <v>1</v>
       </c>
@@ -1465,7 +1474,7 @@
         <v>53</v>
       </c>
     </row>
-    <row r="3" spans="1:3" x14ac:dyDescent="0.25">
+    <row r="3" spans="1:3" x14ac:dyDescent="0.35">
       <c r="A3" s="1">
         <f>A2+1</f>
         <v>2</v>
@@ -1477,9 +1486,9 @@
         <v>17</v>
       </c>
     </row>
-    <row r="4" spans="1:3" x14ac:dyDescent="0.25">
+    <row r="4" spans="1:3" x14ac:dyDescent="0.35">
       <c r="A4" s="1">
-        <f t="shared" ref="A4:A34" si="0">A3+1</f>
+        <f t="shared" ref="A4:A35" si="0">A3+1</f>
         <v>3</v>
       </c>
       <c r="B4" s="1" t="s">
@@ -1489,7 +1498,7 @@
         <v>3</v>
       </c>
     </row>
-    <row r="5" spans="1:3" x14ac:dyDescent="0.25">
+    <row r="5" spans="1:3" x14ac:dyDescent="0.35">
       <c r="A5" s="1">
         <f t="shared" si="0"/>
         <v>4</v>
@@ -1501,7 +1510,7 @@
         <v>5</v>
       </c>
     </row>
-    <row r="6" spans="1:3" x14ac:dyDescent="0.25">
+    <row r="6" spans="1:3" x14ac:dyDescent="0.35">
       <c r="A6" s="1">
         <f t="shared" si="0"/>
         <v>5</v>
@@ -1513,7 +1522,7 @@
         <v>49</v>
       </c>
     </row>
-    <row r="7" spans="1:3" x14ac:dyDescent="0.25">
+    <row r="7" spans="1:3" x14ac:dyDescent="0.35">
       <c r="A7" s="1">
         <f t="shared" si="0"/>
         <v>6</v>
@@ -1525,7 +1534,7 @@
         <v>7</v>
       </c>
     </row>
-    <row r="8" spans="1:3" x14ac:dyDescent="0.25">
+    <row r="8" spans="1:3" x14ac:dyDescent="0.35">
       <c r="A8" s="1">
         <f t="shared" si="0"/>
         <v>7</v>
@@ -1537,7 +1546,7 @@
         <v>51</v>
       </c>
     </row>
-    <row r="9" spans="1:3" ht="14.25" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="9" spans="1:3" ht="14.25" customHeight="1" x14ac:dyDescent="0.35">
       <c r="A9" s="1">
         <f t="shared" si="0"/>
         <v>8</v>
@@ -1549,7 +1558,7 @@
         <v>19</v>
       </c>
     </row>
-    <row r="10" spans="1:3" ht="14.25" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="10" spans="1:3" ht="14.25" customHeight="1" x14ac:dyDescent="0.35">
       <c r="A10" s="1">
         <f t="shared" si="0"/>
         <v>9</v>
@@ -1561,7 +1570,7 @@
         <v>188</v>
       </c>
     </row>
-    <row r="11" spans="1:3" x14ac:dyDescent="0.25">
+    <row r="11" spans="1:3" x14ac:dyDescent="0.35">
       <c r="A11" s="1">
         <f t="shared" si="0"/>
         <v>10</v>
@@ -1573,7 +1582,7 @@
         <v>21</v>
       </c>
     </row>
-    <row r="12" spans="1:3" ht="26.25" x14ac:dyDescent="0.25">
+    <row r="12" spans="1:3" x14ac:dyDescent="0.35">
       <c r="A12" s="1">
         <f t="shared" si="0"/>
         <v>11</v>
@@ -1585,7 +1594,7 @@
         <v>23</v>
       </c>
     </row>
-    <row r="13" spans="1:3" x14ac:dyDescent="0.25">
+    <row r="13" spans="1:3" x14ac:dyDescent="0.35">
       <c r="A13" s="1">
         <f t="shared" si="0"/>
         <v>12</v>
@@ -1597,7 +1606,7 @@
         <v>25</v>
       </c>
     </row>
-    <row r="14" spans="1:3" x14ac:dyDescent="0.25">
+    <row r="14" spans="1:3" x14ac:dyDescent="0.35">
       <c r="A14" s="1">
         <f t="shared" si="0"/>
         <v>13</v>
@@ -1609,7 +1618,7 @@
         <v>27</v>
       </c>
     </row>
-    <row r="15" spans="1:3" x14ac:dyDescent="0.25">
+    <row r="15" spans="1:3" x14ac:dyDescent="0.35">
       <c r="A15" s="1">
         <f t="shared" si="0"/>
         <v>14</v>
@@ -1621,7 +1630,7 @@
         <v>47</v>
       </c>
     </row>
-    <row r="16" spans="1:3" x14ac:dyDescent="0.25">
+    <row r="16" spans="1:3" x14ac:dyDescent="0.35">
       <c r="A16" s="1">
         <f t="shared" si="0"/>
         <v>15</v>
@@ -1633,7 +1642,7 @@
         <v>29</v>
       </c>
     </row>
-    <row r="17" spans="1:3" ht="26.25" x14ac:dyDescent="0.25">
+    <row r="17" spans="1:3" ht="26.5" x14ac:dyDescent="0.35">
       <c r="A17" s="1">
         <f t="shared" si="0"/>
         <v>16</v>
@@ -1645,7 +1654,7 @@
         <v>31</v>
       </c>
     </row>
-    <row r="18" spans="1:3" x14ac:dyDescent="0.25">
+    <row r="18" spans="1:3" x14ac:dyDescent="0.35">
       <c r="A18" s="1">
         <f t="shared" si="0"/>
         <v>17</v>
@@ -1657,7 +1666,7 @@
         <v>9</v>
       </c>
     </row>
-    <row r="19" spans="1:3" x14ac:dyDescent="0.25">
+    <row r="19" spans="1:3" x14ac:dyDescent="0.35">
       <c r="A19" s="1">
         <f t="shared" si="0"/>
         <v>18</v>
@@ -1669,7 +1678,7 @@
         <v>11</v>
       </c>
     </row>
-    <row r="20" spans="1:3" x14ac:dyDescent="0.25">
+    <row r="20" spans="1:3" x14ac:dyDescent="0.35">
       <c r="A20" s="1">
         <f t="shared" si="0"/>
         <v>19</v>
@@ -1681,7 +1690,7 @@
         <v>289</v>
       </c>
     </row>
-    <row r="21" spans="1:3" x14ac:dyDescent="0.25">
+    <row r="21" spans="1:3" x14ac:dyDescent="0.35">
       <c r="A21" s="1">
         <f t="shared" si="0"/>
         <v>20</v>
@@ -1693,7 +1702,7 @@
         <v>176</v>
       </c>
     </row>
-    <row r="22" spans="1:3" x14ac:dyDescent="0.25">
+    <row r="22" spans="1:3" x14ac:dyDescent="0.35">
       <c r="A22" s="1">
         <f t="shared" si="0"/>
         <v>21</v>
@@ -1705,7 +1714,7 @@
         <v>33</v>
       </c>
     </row>
-    <row r="23" spans="1:3" x14ac:dyDescent="0.25">
+    <row r="23" spans="1:3" x14ac:dyDescent="0.35">
       <c r="A23" s="1">
         <f t="shared" si="0"/>
         <v>22</v>
@@ -1717,7 +1726,7 @@
         <v>174</v>
       </c>
     </row>
-    <row r="24" spans="1:3" x14ac:dyDescent="0.25">
+    <row r="24" spans="1:3" x14ac:dyDescent="0.35">
       <c r="A24" s="1">
         <f t="shared" si="0"/>
         <v>23</v>
@@ -1729,7 +1738,7 @@
         <v>13</v>
       </c>
     </row>
-    <row r="25" spans="1:3" x14ac:dyDescent="0.25">
+    <row r="25" spans="1:3" x14ac:dyDescent="0.35">
       <c r="A25" s="1">
         <f t="shared" si="0"/>
         <v>24</v>
@@ -1741,7 +1750,7 @@
         <v>35</v>
       </c>
     </row>
-    <row r="26" spans="1:3" x14ac:dyDescent="0.25">
+    <row r="26" spans="1:3" x14ac:dyDescent="0.35">
       <c r="A26" s="1">
         <f t="shared" si="0"/>
         <v>25</v>
@@ -1753,7 +1762,7 @@
         <v>186</v>
       </c>
     </row>
-    <row r="27" spans="1:3" x14ac:dyDescent="0.25">
+    <row r="27" spans="1:3" x14ac:dyDescent="0.35">
       <c r="A27" s="1">
         <f t="shared" si="0"/>
         <v>26</v>
@@ -1765,7 +1774,7 @@
         <v>15</v>
       </c>
     </row>
-    <row r="28" spans="1:3" x14ac:dyDescent="0.25">
+    <row r="28" spans="1:3" x14ac:dyDescent="0.35">
       <c r="A28" s="1">
         <f t="shared" si="0"/>
         <v>27</v>
@@ -1777,7 +1786,7 @@
         <v>167</v>
       </c>
     </row>
-    <row r="29" spans="1:3" x14ac:dyDescent="0.25">
+    <row r="29" spans="1:3" x14ac:dyDescent="0.35">
       <c r="A29" s="1">
         <f t="shared" si="0"/>
         <v>28</v>
@@ -1789,7 +1798,7 @@
         <v>37</v>
       </c>
     </row>
-    <row r="30" spans="1:3" x14ac:dyDescent="0.25">
+    <row r="30" spans="1:3" x14ac:dyDescent="0.35">
       <c r="A30" s="1">
         <f t="shared" si="0"/>
         <v>29</v>
@@ -1801,7 +1810,7 @@
         <v>41</v>
       </c>
     </row>
-    <row r="31" spans="1:3" x14ac:dyDescent="0.25">
+    <row r="31" spans="1:3" x14ac:dyDescent="0.35">
       <c r="A31" s="1">
         <f t="shared" si="0"/>
         <v>30</v>
@@ -1813,7 +1822,7 @@
         <v>43</v>
       </c>
     </row>
-    <row r="32" spans="1:3" x14ac:dyDescent="0.25">
+    <row r="32" spans="1:3" x14ac:dyDescent="0.35">
       <c r="A32" s="1">
         <f t="shared" si="0"/>
         <v>31</v>
@@ -1825,7 +1834,7 @@
         <v>45</v>
       </c>
     </row>
-    <row r="33" spans="1:3" x14ac:dyDescent="0.25">
+    <row r="33" spans="1:3" x14ac:dyDescent="0.35">
       <c r="A33" s="1">
         <f t="shared" si="0"/>
         <v>32</v>
@@ -1837,7 +1846,7 @@
         <v>182</v>
       </c>
     </row>
-    <row r="34" spans="1:3" x14ac:dyDescent="0.25">
+    <row r="34" spans="1:3" x14ac:dyDescent="0.35">
       <c r="A34" s="1">
         <f t="shared" si="0"/>
         <v>33</v>
@@ -1847,6 +1856,18 @@
       </c>
       <c r="C34" s="1" t="s">
         <v>39</v>
+      </c>
+    </row>
+    <row r="35" spans="1:3" x14ac:dyDescent="0.35">
+      <c r="A35" s="1">
+        <f t="shared" si="0"/>
+        <v>34</v>
+      </c>
+      <c r="B35" s="1" t="s">
+        <v>294</v>
+      </c>
+      <c r="C35" s="1" t="s">
+        <v>295</v>
       </c>
     </row>
   </sheetData>
@@ -1855,17 +1876,18 @@
       <sortCondition ref="B1:B34"/>
     </sortState>
   </autoFilter>
-  <conditionalFormatting sqref="B25:B26">
-    <cfRule type="duplicateValues" dxfId="9" priority="5"/>
+  <phoneticPr fontId="3" type="noConversion"/>
+  <conditionalFormatting sqref="B20">
+    <cfRule type="duplicateValues" dxfId="9" priority="1"/>
   </conditionalFormatting>
   <conditionalFormatting sqref="B23">
     <cfRule type="duplicateValues" dxfId="8" priority="3"/>
   </conditionalFormatting>
+  <conditionalFormatting sqref="B25:B26">
+    <cfRule type="duplicateValues" dxfId="7" priority="5"/>
+  </conditionalFormatting>
   <conditionalFormatting sqref="B33">
-    <cfRule type="duplicateValues" dxfId="7" priority="2"/>
-  </conditionalFormatting>
-  <conditionalFormatting sqref="B20">
-    <cfRule type="duplicateValues" dxfId="6" priority="1"/>
+    <cfRule type="duplicateValues" dxfId="6" priority="2"/>
   </conditionalFormatting>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
 </worksheet>
@@ -1874,13 +1896,13 @@
 <file path=xl/worksheets/sheet2.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{EDC1EDC2-6D0F-4810-970C-A3BE3A1678B9}">
   <dimension ref="A1:C64"/>
-  <sheetFormatPr defaultRowHeight="15" x14ac:dyDescent="0.25"/>
+  <sheetFormatPr defaultRowHeight="14.5" x14ac:dyDescent="0.35"/>
   <cols>
     <col min="1" max="2" width="7" style="3" bestFit="1" customWidth="1"/>
-    <col min="3" max="3" width="25.7109375" style="3" bestFit="1" customWidth="1"/>
+    <col min="3" max="3" width="25.7265625" style="3" bestFit="1" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:3" x14ac:dyDescent="0.25">
+    <row r="1" spans="1:3" x14ac:dyDescent="0.35">
       <c r="A1" s="2" t="s">
         <v>172</v>
       </c>
@@ -1891,7 +1913,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="2" spans="1:3" x14ac:dyDescent="0.25">
+    <row r="2" spans="1:3" x14ac:dyDescent="0.35">
       <c r="A2" s="2">
         <v>1</v>
       </c>
@@ -1902,7 +1924,7 @@
         <v>55</v>
       </c>
     </row>
-    <row r="3" spans="1:3" x14ac:dyDescent="0.25">
+    <row r="3" spans="1:3" x14ac:dyDescent="0.35">
       <c r="A3" s="2">
         <f>A2+1</f>
         <v>2</v>
@@ -1914,7 +1936,7 @@
         <v>57</v>
       </c>
     </row>
-    <row r="4" spans="1:3" x14ac:dyDescent="0.25">
+    <row r="4" spans="1:3" x14ac:dyDescent="0.35">
       <c r="A4" s="2">
         <f t="shared" ref="A4:A64" si="0">A3+1</f>
         <v>3</v>
@@ -1926,7 +1948,7 @@
         <v>59</v>
       </c>
     </row>
-    <row r="5" spans="1:3" x14ac:dyDescent="0.25">
+    <row r="5" spans="1:3" x14ac:dyDescent="0.35">
       <c r="A5" s="2">
         <f t="shared" si="0"/>
         <v>4</v>
@@ -1938,7 +1960,7 @@
         <v>61</v>
       </c>
     </row>
-    <row r="6" spans="1:3" x14ac:dyDescent="0.25">
+    <row r="6" spans="1:3" x14ac:dyDescent="0.35">
       <c r="A6" s="2">
         <f t="shared" si="0"/>
         <v>5</v>
@@ -1950,7 +1972,7 @@
         <v>63</v>
       </c>
     </row>
-    <row r="7" spans="1:3" x14ac:dyDescent="0.25">
+    <row r="7" spans="1:3" x14ac:dyDescent="0.35">
       <c r="A7" s="2">
         <f t="shared" si="0"/>
         <v>6</v>
@@ -1962,7 +1984,7 @@
         <v>65</v>
       </c>
     </row>
-    <row r="8" spans="1:3" x14ac:dyDescent="0.25">
+    <row r="8" spans="1:3" x14ac:dyDescent="0.35">
       <c r="A8" s="2">
         <f t="shared" si="0"/>
         <v>7</v>
@@ -1974,7 +1996,7 @@
         <v>67</v>
       </c>
     </row>
-    <row r="9" spans="1:3" x14ac:dyDescent="0.25">
+    <row r="9" spans="1:3" x14ac:dyDescent="0.35">
       <c r="A9" s="2">
         <f t="shared" si="0"/>
         <v>8</v>
@@ -1986,7 +2008,7 @@
         <v>69</v>
       </c>
     </row>
-    <row r="10" spans="1:3" x14ac:dyDescent="0.25">
+    <row r="10" spans="1:3" x14ac:dyDescent="0.35">
       <c r="A10" s="2">
         <f t="shared" si="0"/>
         <v>9</v>
@@ -1998,7 +2020,7 @@
         <v>71</v>
       </c>
     </row>
-    <row r="11" spans="1:3" x14ac:dyDescent="0.25">
+    <row r="11" spans="1:3" x14ac:dyDescent="0.35">
       <c r="A11" s="2">
         <f t="shared" si="0"/>
         <v>10</v>
@@ -2010,7 +2032,7 @@
         <v>73</v>
       </c>
     </row>
-    <row r="12" spans="1:3" x14ac:dyDescent="0.25">
+    <row r="12" spans="1:3" x14ac:dyDescent="0.35">
       <c r="A12" s="2">
         <f t="shared" si="0"/>
         <v>11</v>
@@ -2022,7 +2044,7 @@
         <v>75</v>
       </c>
     </row>
-    <row r="13" spans="1:3" x14ac:dyDescent="0.25">
+    <row r="13" spans="1:3" x14ac:dyDescent="0.35">
       <c r="A13" s="2">
         <f t="shared" si="0"/>
         <v>12</v>
@@ -2034,7 +2056,7 @@
         <v>180</v>
       </c>
     </row>
-    <row r="14" spans="1:3" x14ac:dyDescent="0.25">
+    <row r="14" spans="1:3" x14ac:dyDescent="0.35">
       <c r="A14" s="2">
         <f t="shared" si="0"/>
         <v>13</v>
@@ -2046,7 +2068,7 @@
         <v>77</v>
       </c>
     </row>
-    <row r="15" spans="1:3" x14ac:dyDescent="0.25">
+    <row r="15" spans="1:3" x14ac:dyDescent="0.35">
       <c r="A15" s="2">
         <f t="shared" si="0"/>
         <v>14</v>
@@ -2058,7 +2080,7 @@
         <v>79</v>
       </c>
     </row>
-    <row r="16" spans="1:3" x14ac:dyDescent="0.25">
+    <row r="16" spans="1:3" x14ac:dyDescent="0.35">
       <c r="A16" s="2">
         <f t="shared" si="0"/>
         <v>15</v>
@@ -2070,7 +2092,7 @@
         <v>81</v>
       </c>
     </row>
-    <row r="17" spans="1:3" x14ac:dyDescent="0.25">
+    <row r="17" spans="1:3" x14ac:dyDescent="0.35">
       <c r="A17" s="2">
         <f t="shared" si="0"/>
         <v>16</v>
@@ -2082,7 +2104,7 @@
         <v>184</v>
       </c>
     </row>
-    <row r="18" spans="1:3" x14ac:dyDescent="0.25">
+    <row r="18" spans="1:3" x14ac:dyDescent="0.35">
       <c r="A18" s="2">
         <f t="shared" si="0"/>
         <v>17</v>
@@ -2094,7 +2116,7 @@
         <v>83</v>
       </c>
     </row>
-    <row r="19" spans="1:3" x14ac:dyDescent="0.25">
+    <row r="19" spans="1:3" x14ac:dyDescent="0.35">
       <c r="A19" s="2">
         <f t="shared" si="0"/>
         <v>18</v>
@@ -2106,7 +2128,7 @@
         <v>85</v>
       </c>
     </row>
-    <row r="20" spans="1:3" x14ac:dyDescent="0.25">
+    <row r="20" spans="1:3" x14ac:dyDescent="0.35">
       <c r="A20" s="2">
         <f t="shared" si="0"/>
         <v>19</v>
@@ -2118,7 +2140,7 @@
         <v>87</v>
       </c>
     </row>
-    <row r="21" spans="1:3" x14ac:dyDescent="0.25">
+    <row r="21" spans="1:3" x14ac:dyDescent="0.35">
       <c r="A21" s="2">
         <f t="shared" si="0"/>
         <v>20</v>
@@ -2130,7 +2152,7 @@
         <v>89</v>
       </c>
     </row>
-    <row r="22" spans="1:3" x14ac:dyDescent="0.25">
+    <row r="22" spans="1:3" x14ac:dyDescent="0.35">
       <c r="A22" s="2">
         <f t="shared" si="0"/>
         <v>21</v>
@@ -2142,7 +2164,7 @@
         <v>91</v>
       </c>
     </row>
-    <row r="23" spans="1:3" x14ac:dyDescent="0.25">
+    <row r="23" spans="1:3" x14ac:dyDescent="0.35">
       <c r="A23" s="2">
         <f t="shared" si="0"/>
         <v>22</v>
@@ -2154,7 +2176,7 @@
         <v>93</v>
       </c>
     </row>
-    <row r="24" spans="1:3" x14ac:dyDescent="0.25">
+    <row r="24" spans="1:3" x14ac:dyDescent="0.35">
       <c r="A24" s="2">
         <f t="shared" si="0"/>
         <v>23</v>
@@ -2166,7 +2188,7 @@
         <v>292</v>
       </c>
     </row>
-    <row r="25" spans="1:3" x14ac:dyDescent="0.25">
+    <row r="25" spans="1:3" x14ac:dyDescent="0.35">
       <c r="A25" s="2">
         <f t="shared" si="0"/>
         <v>24</v>
@@ -2178,7 +2200,7 @@
         <v>95</v>
       </c>
     </row>
-    <row r="26" spans="1:3" x14ac:dyDescent="0.25">
+    <row r="26" spans="1:3" x14ac:dyDescent="0.35">
       <c r="A26" s="2">
         <f t="shared" si="0"/>
         <v>25</v>
@@ -2190,7 +2212,7 @@
         <v>97</v>
       </c>
     </row>
-    <row r="27" spans="1:3" x14ac:dyDescent="0.25">
+    <row r="27" spans="1:3" x14ac:dyDescent="0.35">
       <c r="A27" s="2">
         <f t="shared" si="0"/>
         <v>26</v>
@@ -2202,7 +2224,7 @@
         <v>169</v>
       </c>
     </row>
-    <row r="28" spans="1:3" x14ac:dyDescent="0.25">
+    <row r="28" spans="1:3" x14ac:dyDescent="0.35">
       <c r="A28" s="2">
         <f t="shared" si="0"/>
         <v>27</v>
@@ -2214,7 +2236,7 @@
         <v>99</v>
       </c>
     </row>
-    <row r="29" spans="1:3" x14ac:dyDescent="0.25">
+    <row r="29" spans="1:3" x14ac:dyDescent="0.35">
       <c r="A29" s="2">
         <f t="shared" si="0"/>
         <v>28</v>
@@ -2226,7 +2248,7 @@
         <v>101</v>
       </c>
     </row>
-    <row r="30" spans="1:3" x14ac:dyDescent="0.25">
+    <row r="30" spans="1:3" x14ac:dyDescent="0.35">
       <c r="A30" s="2">
         <f t="shared" si="0"/>
         <v>29</v>
@@ -2238,7 +2260,7 @@
         <v>103</v>
       </c>
     </row>
-    <row r="31" spans="1:3" x14ac:dyDescent="0.25">
+    <row r="31" spans="1:3" x14ac:dyDescent="0.35">
       <c r="A31" s="2">
         <f t="shared" si="0"/>
         <v>30</v>
@@ -2250,7 +2272,7 @@
         <v>105</v>
       </c>
     </row>
-    <row r="32" spans="1:3" x14ac:dyDescent="0.25">
+    <row r="32" spans="1:3" x14ac:dyDescent="0.35">
       <c r="A32" s="2">
         <f t="shared" si="0"/>
         <v>31</v>
@@ -2262,7 +2284,7 @@
         <v>286</v>
       </c>
     </row>
-    <row r="33" spans="1:3" x14ac:dyDescent="0.25">
+    <row r="33" spans="1:3" x14ac:dyDescent="0.35">
       <c r="A33" s="2">
         <f t="shared" si="0"/>
         <v>32</v>
@@ -2274,7 +2296,7 @@
         <v>107</v>
       </c>
     </row>
-    <row r="34" spans="1:3" x14ac:dyDescent="0.25">
+    <row r="34" spans="1:3" x14ac:dyDescent="0.35">
       <c r="A34" s="2">
         <f t="shared" si="0"/>
         <v>33</v>
@@ -2286,7 +2308,7 @@
         <v>109</v>
       </c>
     </row>
-    <row r="35" spans="1:3" x14ac:dyDescent="0.25">
+    <row r="35" spans="1:3" x14ac:dyDescent="0.35">
       <c r="A35" s="2">
         <f t="shared" si="0"/>
         <v>34</v>
@@ -2298,7 +2320,7 @@
         <v>111</v>
       </c>
     </row>
-    <row r="36" spans="1:3" x14ac:dyDescent="0.25">
+    <row r="36" spans="1:3" x14ac:dyDescent="0.35">
       <c r="A36" s="2">
         <f t="shared" si="0"/>
         <v>35</v>
@@ -2310,7 +2332,7 @@
         <v>113</v>
       </c>
     </row>
-    <row r="37" spans="1:3" x14ac:dyDescent="0.25">
+    <row r="37" spans="1:3" x14ac:dyDescent="0.35">
       <c r="A37" s="2">
         <f t="shared" si="0"/>
         <v>36</v>
@@ -2322,7 +2344,7 @@
         <v>115</v>
       </c>
     </row>
-    <row r="38" spans="1:3" x14ac:dyDescent="0.25">
+    <row r="38" spans="1:3" x14ac:dyDescent="0.35">
       <c r="A38" s="2">
         <f t="shared" si="0"/>
         <v>37</v>
@@ -2334,7 +2356,7 @@
         <v>117</v>
       </c>
     </row>
-    <row r="39" spans="1:3" x14ac:dyDescent="0.25">
+    <row r="39" spans="1:3" x14ac:dyDescent="0.35">
       <c r="A39" s="2">
         <f t="shared" si="0"/>
         <v>38</v>
@@ -2346,7 +2368,7 @@
         <v>119</v>
       </c>
     </row>
-    <row r="40" spans="1:3" x14ac:dyDescent="0.25">
+    <row r="40" spans="1:3" x14ac:dyDescent="0.35">
       <c r="A40" s="2">
         <f t="shared" si="0"/>
         <v>39</v>
@@ -2358,7 +2380,7 @@
         <v>121</v>
       </c>
     </row>
-    <row r="41" spans="1:3" x14ac:dyDescent="0.25">
+    <row r="41" spans="1:3" x14ac:dyDescent="0.35">
       <c r="A41" s="2">
         <f t="shared" si="0"/>
         <v>40</v>
@@ -2370,7 +2392,7 @@
         <v>123</v>
       </c>
     </row>
-    <row r="42" spans="1:3" x14ac:dyDescent="0.25">
+    <row r="42" spans="1:3" x14ac:dyDescent="0.35">
       <c r="A42" s="2">
         <f t="shared" si="0"/>
         <v>41</v>
@@ -2382,7 +2404,7 @@
         <v>125</v>
       </c>
     </row>
-    <row r="43" spans="1:3" x14ac:dyDescent="0.25">
+    <row r="43" spans="1:3" x14ac:dyDescent="0.35">
       <c r="A43" s="2">
         <f t="shared" si="0"/>
         <v>42</v>
@@ -2394,7 +2416,7 @@
         <v>127</v>
       </c>
     </row>
-    <row r="44" spans="1:3" x14ac:dyDescent="0.25">
+    <row r="44" spans="1:3" x14ac:dyDescent="0.35">
       <c r="A44" s="2">
         <f t="shared" si="0"/>
         <v>43</v>
@@ -2406,7 +2428,7 @@
         <v>129</v>
       </c>
     </row>
-    <row r="45" spans="1:3" x14ac:dyDescent="0.25">
+    <row r="45" spans="1:3" x14ac:dyDescent="0.35">
       <c r="A45" s="2">
         <f t="shared" si="0"/>
         <v>44</v>
@@ -2418,7 +2440,7 @@
         <v>131</v>
       </c>
     </row>
-    <row r="46" spans="1:3" x14ac:dyDescent="0.25">
+    <row r="46" spans="1:3" x14ac:dyDescent="0.35">
       <c r="A46" s="2">
         <f t="shared" si="0"/>
         <v>45</v>
@@ -2430,7 +2452,7 @@
         <v>133</v>
       </c>
     </row>
-    <row r="47" spans="1:3" x14ac:dyDescent="0.25">
+    <row r="47" spans="1:3" x14ac:dyDescent="0.35">
       <c r="A47" s="2">
         <f t="shared" si="0"/>
         <v>46</v>
@@ -2442,7 +2464,7 @@
         <v>135</v>
       </c>
     </row>
-    <row r="48" spans="1:3" x14ac:dyDescent="0.25">
+    <row r="48" spans="1:3" x14ac:dyDescent="0.35">
       <c r="A48" s="2">
         <f t="shared" si="0"/>
         <v>47</v>
@@ -2454,7 +2476,7 @@
         <v>137</v>
       </c>
     </row>
-    <row r="49" spans="1:3" x14ac:dyDescent="0.25">
+    <row r="49" spans="1:3" x14ac:dyDescent="0.35">
       <c r="A49" s="2">
         <f t="shared" si="0"/>
         <v>48</v>
@@ -2466,7 +2488,7 @@
         <v>139</v>
       </c>
     </row>
-    <row r="50" spans="1:3" x14ac:dyDescent="0.25">
+    <row r="50" spans="1:3" x14ac:dyDescent="0.35">
       <c r="A50" s="2">
         <f t="shared" si="0"/>
         <v>49</v>
@@ -2478,7 +2500,7 @@
         <v>141</v>
       </c>
     </row>
-    <row r="51" spans="1:3" x14ac:dyDescent="0.25">
+    <row r="51" spans="1:3" x14ac:dyDescent="0.35">
       <c r="A51" s="2">
         <f t="shared" si="0"/>
         <v>50</v>
@@ -2490,7 +2512,7 @@
         <v>143</v>
       </c>
     </row>
-    <row r="52" spans="1:3" x14ac:dyDescent="0.25">
+    <row r="52" spans="1:3" x14ac:dyDescent="0.35">
       <c r="A52" s="2">
         <f t="shared" si="0"/>
         <v>51</v>
@@ -2502,7 +2524,7 @@
         <v>145</v>
       </c>
     </row>
-    <row r="53" spans="1:3" x14ac:dyDescent="0.25">
+    <row r="53" spans="1:3" x14ac:dyDescent="0.35">
       <c r="A53" s="2">
         <f t="shared" si="0"/>
         <v>52</v>
@@ -2514,7 +2536,7 @@
         <v>178</v>
       </c>
     </row>
-    <row r="54" spans="1:3" x14ac:dyDescent="0.25">
+    <row r="54" spans="1:3" x14ac:dyDescent="0.35">
       <c r="A54" s="2">
         <f t="shared" si="0"/>
         <v>53</v>
@@ -2526,7 +2548,7 @@
         <v>147</v>
       </c>
     </row>
-    <row r="55" spans="1:3" x14ac:dyDescent="0.25">
+    <row r="55" spans="1:3" x14ac:dyDescent="0.35">
       <c r="A55" s="2">
         <f t="shared" si="0"/>
         <v>54</v>
@@ -2538,7 +2560,7 @@
         <v>149</v>
       </c>
     </row>
-    <row r="56" spans="1:3" x14ac:dyDescent="0.25">
+    <row r="56" spans="1:3" x14ac:dyDescent="0.35">
       <c r="A56" s="2">
         <f t="shared" si="0"/>
         <v>55</v>
@@ -2550,7 +2572,7 @@
         <v>151</v>
       </c>
     </row>
-    <row r="57" spans="1:3" x14ac:dyDescent="0.25">
+    <row r="57" spans="1:3" x14ac:dyDescent="0.35">
       <c r="A57" s="2">
         <f t="shared" si="0"/>
         <v>56</v>
@@ -2562,7 +2584,7 @@
         <v>153</v>
       </c>
     </row>
-    <row r="58" spans="1:3" x14ac:dyDescent="0.25">
+    <row r="58" spans="1:3" x14ac:dyDescent="0.35">
       <c r="A58" s="2">
         <f t="shared" si="0"/>
         <v>57</v>
@@ -2574,7 +2596,7 @@
         <v>155</v>
       </c>
     </row>
-    <row r="59" spans="1:3" x14ac:dyDescent="0.25">
+    <row r="59" spans="1:3" x14ac:dyDescent="0.35">
       <c r="A59" s="2">
         <f t="shared" si="0"/>
         <v>58</v>
@@ -2586,7 +2608,7 @@
         <v>157</v>
       </c>
     </row>
-    <row r="60" spans="1:3" x14ac:dyDescent="0.25">
+    <row r="60" spans="1:3" x14ac:dyDescent="0.35">
       <c r="A60" s="2">
         <f t="shared" si="0"/>
         <v>59</v>
@@ -2598,7 +2620,7 @@
         <v>171</v>
       </c>
     </row>
-    <row r="61" spans="1:3" x14ac:dyDescent="0.25">
+    <row r="61" spans="1:3" x14ac:dyDescent="0.35">
       <c r="A61" s="2">
         <f t="shared" si="0"/>
         <v>60</v>
@@ -2610,7 +2632,7 @@
         <v>159</v>
       </c>
     </row>
-    <row r="62" spans="1:3" x14ac:dyDescent="0.25">
+    <row r="62" spans="1:3" x14ac:dyDescent="0.35">
       <c r="A62" s="2">
         <f t="shared" si="0"/>
         <v>61</v>
@@ -2622,7 +2644,7 @@
         <v>161</v>
       </c>
     </row>
-    <row r="63" spans="1:3" x14ac:dyDescent="0.25">
+    <row r="63" spans="1:3" x14ac:dyDescent="0.35">
       <c r="A63" s="2">
         <f t="shared" si="0"/>
         <v>62</v>
@@ -2634,7 +2656,7 @@
         <v>163</v>
       </c>
     </row>
-    <row r="64" spans="1:3" x14ac:dyDescent="0.25">
+    <row r="64" spans="1:3" x14ac:dyDescent="0.35">
       <c r="A64" s="2">
         <f t="shared" si="0"/>
         <v>63</v>
@@ -2653,7 +2675,7 @@
     </sortState>
   </autoFilter>
   <conditionalFormatting sqref="B24">
-    <cfRule type="duplicateValues" dxfId="1" priority="1"/>
+    <cfRule type="duplicateValues" dxfId="5" priority="1"/>
   </conditionalFormatting>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
 </worksheet>
@@ -2662,15 +2684,15 @@
 <file path=xl/worksheets/sheet3.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{591939A9-D768-41A1-9DEC-2A499486FE46}">
   <dimension ref="A1:E97"/>
-  <sheetFormatPr defaultRowHeight="15" x14ac:dyDescent="0.25"/>
+  <sheetFormatPr defaultRowHeight="14.5" x14ac:dyDescent="0.35"/>
   <cols>
     <col min="1" max="2" width="10" customWidth="1"/>
-    <col min="3" max="3" width="18.42578125" customWidth="1"/>
-    <col min="4" max="4" width="29.140625" customWidth="1"/>
-    <col min="5" max="5" width="24.42578125" customWidth="1"/>
+    <col min="3" max="3" width="18.453125" customWidth="1"/>
+    <col min="4" max="4" width="29.1796875" customWidth="1"/>
+    <col min="5" max="5" width="24.453125" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:5" x14ac:dyDescent="0.25">
+    <row r="1" spans="1:5" x14ac:dyDescent="0.35">
       <c r="A1" s="1" t="s">
         <v>172</v>
       </c>
@@ -2687,7 +2709,7 @@
         <v>190</v>
       </c>
     </row>
-    <row r="2" spans="1:5" ht="30" x14ac:dyDescent="0.25">
+    <row r="2" spans="1:5" x14ac:dyDescent="0.35">
       <c r="A2" s="2">
         <v>1</v>
       </c>
@@ -2704,7 +2726,7 @@
         <v>284</v>
       </c>
     </row>
-    <row r="3" spans="1:5" ht="30" x14ac:dyDescent="0.25">
+    <row r="3" spans="1:5" x14ac:dyDescent="0.35">
       <c r="A3" s="2">
         <v>2</v>
       </c>
@@ -2721,7 +2743,7 @@
         <v>284</v>
       </c>
     </row>
-    <row r="4" spans="1:5" ht="30" x14ac:dyDescent="0.25">
+    <row r="4" spans="1:5" x14ac:dyDescent="0.35">
       <c r="A4" s="2">
         <v>3</v>
       </c>
@@ -2738,7 +2760,7 @@
         <v>284</v>
       </c>
     </row>
-    <row r="5" spans="1:5" ht="30" x14ac:dyDescent="0.25">
+    <row r="5" spans="1:5" x14ac:dyDescent="0.35">
       <c r="A5" s="2">
         <v>4</v>
       </c>
@@ -2755,7 +2777,7 @@
         <v>284</v>
       </c>
     </row>
-    <row r="6" spans="1:5" ht="30" x14ac:dyDescent="0.25">
+    <row r="6" spans="1:5" x14ac:dyDescent="0.35">
       <c r="A6" s="2">
         <v>5</v>
       </c>
@@ -2772,7 +2794,7 @@
         <v>284</v>
       </c>
     </row>
-    <row r="7" spans="1:5" ht="30" x14ac:dyDescent="0.25">
+    <row r="7" spans="1:5" x14ac:dyDescent="0.35">
       <c r="A7" s="2">
         <v>6</v>
       </c>
@@ -2789,7 +2811,7 @@
         <v>284</v>
       </c>
     </row>
-    <row r="8" spans="1:5" ht="30" x14ac:dyDescent="0.25">
+    <row r="8" spans="1:5" x14ac:dyDescent="0.35">
       <c r="A8" s="2">
         <v>7</v>
       </c>
@@ -2806,7 +2828,7 @@
         <v>284</v>
       </c>
     </row>
-    <row r="9" spans="1:5" ht="14.25" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="9" spans="1:5" ht="14.25" customHeight="1" x14ac:dyDescent="0.35">
       <c r="A9" s="2">
         <v>8</v>
       </c>
@@ -2823,7 +2845,7 @@
         <v>284</v>
       </c>
     </row>
-    <row r="10" spans="1:5" ht="14.25" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="10" spans="1:5" ht="14.25" customHeight="1" x14ac:dyDescent="0.35">
       <c r="A10" s="2">
         <v>9</v>
       </c>
@@ -2840,7 +2862,7 @@
         <v>284</v>
       </c>
     </row>
-    <row r="11" spans="1:5" ht="30" x14ac:dyDescent="0.25">
+    <row r="11" spans="1:5" x14ac:dyDescent="0.35">
       <c r="A11" s="2">
         <v>10</v>
       </c>
@@ -2857,7 +2879,7 @@
         <v>284</v>
       </c>
     </row>
-    <row r="12" spans="1:5" ht="30" x14ac:dyDescent="0.25">
+    <row r="12" spans="1:5" x14ac:dyDescent="0.35">
       <c r="A12" s="2">
         <v>11</v>
       </c>
@@ -2874,7 +2896,7 @@
         <v>284</v>
       </c>
     </row>
-    <row r="13" spans="1:5" ht="30" x14ac:dyDescent="0.25">
+    <row r="13" spans="1:5" x14ac:dyDescent="0.35">
       <c r="A13" s="2">
         <v>12</v>
       </c>
@@ -2891,7 +2913,7 @@
         <v>284</v>
       </c>
     </row>
-    <row r="14" spans="1:5" x14ac:dyDescent="0.25">
+    <row r="14" spans="1:5" x14ac:dyDescent="0.35">
       <c r="A14" s="2">
         <v>13</v>
       </c>
@@ -2908,7 +2930,7 @@
         <v>284</v>
       </c>
     </row>
-    <row r="15" spans="1:5" x14ac:dyDescent="0.25">
+    <row r="15" spans="1:5" x14ac:dyDescent="0.35">
       <c r="A15" s="2">
         <v>14</v>
       </c>
@@ -2925,7 +2947,7 @@
         <v>284</v>
       </c>
     </row>
-    <row r="16" spans="1:5" x14ac:dyDescent="0.25">
+    <row r="16" spans="1:5" x14ac:dyDescent="0.35">
       <c r="A16" s="2">
         <v>15</v>
       </c>
@@ -2942,7 +2964,7 @@
         <v>284</v>
       </c>
     </row>
-    <row r="17" spans="1:5" ht="26.25" x14ac:dyDescent="0.25">
+    <row r="17" spans="1:5" ht="26.5" x14ac:dyDescent="0.35">
       <c r="A17" s="2">
         <v>16</v>
       </c>
@@ -2959,7 +2981,7 @@
         <v>284</v>
       </c>
     </row>
-    <row r="18" spans="1:5" x14ac:dyDescent="0.25">
+    <row r="18" spans="1:5" x14ac:dyDescent="0.35">
       <c r="A18" s="2">
         <v>17</v>
       </c>
@@ -2976,7 +2998,7 @@
         <v>284</v>
       </c>
     </row>
-    <row r="19" spans="1:5" x14ac:dyDescent="0.25">
+    <row r="19" spans="1:5" x14ac:dyDescent="0.35">
       <c r="A19" s="2">
         <v>18</v>
       </c>
@@ -2993,7 +3015,7 @@
         <v>284</v>
       </c>
     </row>
-    <row r="20" spans="1:5" x14ac:dyDescent="0.25">
+    <row r="20" spans="1:5" x14ac:dyDescent="0.35">
       <c r="A20" s="2">
         <v>19</v>
       </c>
@@ -3010,7 +3032,7 @@
         <v>284</v>
       </c>
     </row>
-    <row r="21" spans="1:5" x14ac:dyDescent="0.25">
+    <row r="21" spans="1:5" x14ac:dyDescent="0.35">
       <c r="A21" s="2">
         <v>20</v>
       </c>
@@ -3027,7 +3049,7 @@
         <v>284</v>
       </c>
     </row>
-    <row r="22" spans="1:5" x14ac:dyDescent="0.25">
+    <row r="22" spans="1:5" x14ac:dyDescent="0.35">
       <c r="A22" s="2">
         <v>21</v>
       </c>
@@ -3044,7 +3066,7 @@
         <v>284</v>
       </c>
     </row>
-    <row r="23" spans="1:5" x14ac:dyDescent="0.25">
+    <row r="23" spans="1:5" x14ac:dyDescent="0.35">
       <c r="A23" s="2">
         <v>22</v>
       </c>
@@ -3061,7 +3083,7 @@
         <v>284</v>
       </c>
     </row>
-    <row r="24" spans="1:5" x14ac:dyDescent="0.25">
+    <row r="24" spans="1:5" x14ac:dyDescent="0.35">
       <c r="A24" s="2">
         <v>23</v>
       </c>
@@ -3078,7 +3100,7 @@
         <v>284</v>
       </c>
     </row>
-    <row r="25" spans="1:5" x14ac:dyDescent="0.25">
+    <row r="25" spans="1:5" x14ac:dyDescent="0.35">
       <c r="A25" s="2">
         <v>24</v>
       </c>
@@ -3095,7 +3117,7 @@
         <v>284</v>
       </c>
     </row>
-    <row r="26" spans="1:5" x14ac:dyDescent="0.25">
+    <row r="26" spans="1:5" x14ac:dyDescent="0.35">
       <c r="A26" s="2">
         <v>25</v>
       </c>
@@ -3112,7 +3134,7 @@
         <v>284</v>
       </c>
     </row>
-    <row r="27" spans="1:5" x14ac:dyDescent="0.25">
+    <row r="27" spans="1:5" x14ac:dyDescent="0.35">
       <c r="A27" s="2">
         <v>26</v>
       </c>
@@ -3129,7 +3151,7 @@
         <v>284</v>
       </c>
     </row>
-    <row r="28" spans="1:5" x14ac:dyDescent="0.25">
+    <row r="28" spans="1:5" x14ac:dyDescent="0.35">
       <c r="A28" s="2">
         <v>27</v>
       </c>
@@ -3146,7 +3168,7 @@
         <v>284</v>
       </c>
     </row>
-    <row r="29" spans="1:5" x14ac:dyDescent="0.25">
+    <row r="29" spans="1:5" x14ac:dyDescent="0.35">
       <c r="A29" s="2">
         <v>28</v>
       </c>
@@ -3163,7 +3185,7 @@
         <v>284</v>
       </c>
     </row>
-    <row r="30" spans="1:5" x14ac:dyDescent="0.25">
+    <row r="30" spans="1:5" x14ac:dyDescent="0.35">
       <c r="A30" s="2">
         <v>29</v>
       </c>
@@ -3180,7 +3202,7 @@
         <v>284</v>
       </c>
     </row>
-    <row r="31" spans="1:5" x14ac:dyDescent="0.25">
+    <row r="31" spans="1:5" x14ac:dyDescent="0.35">
       <c r="A31" s="2">
         <v>30</v>
       </c>
@@ -3197,7 +3219,7 @@
         <v>284</v>
       </c>
     </row>
-    <row r="32" spans="1:5" x14ac:dyDescent="0.25">
+    <row r="32" spans="1:5" x14ac:dyDescent="0.35">
       <c r="A32" s="2">
         <v>31</v>
       </c>
@@ -3214,7 +3236,7 @@
         <v>284</v>
       </c>
     </row>
-    <row r="33" spans="1:5" x14ac:dyDescent="0.25">
+    <row r="33" spans="1:5" x14ac:dyDescent="0.35">
       <c r="A33" s="4">
         <v>32</v>
       </c>
@@ -3231,7 +3253,7 @@
         <v>284</v>
       </c>
     </row>
-    <row r="34" spans="1:5" x14ac:dyDescent="0.25">
+    <row r="34" spans="1:5" x14ac:dyDescent="0.35">
       <c r="A34" s="2">
         <v>33</v>
       </c>
@@ -3248,7 +3270,7 @@
         <v>284</v>
       </c>
     </row>
-    <row r="35" spans="1:5" x14ac:dyDescent="0.25">
+    <row r="35" spans="1:5" x14ac:dyDescent="0.35">
       <c r="A35" s="2">
         <v>34</v>
       </c>
@@ -3265,7 +3287,7 @@
         <v>284</v>
       </c>
     </row>
-    <row r="36" spans="1:5" x14ac:dyDescent="0.25">
+    <row r="36" spans="1:5" x14ac:dyDescent="0.35">
       <c r="A36" s="2">
         <v>35</v>
       </c>
@@ -3282,7 +3304,7 @@
         <v>284</v>
       </c>
     </row>
-    <row r="37" spans="1:5" x14ac:dyDescent="0.25">
+    <row r="37" spans="1:5" x14ac:dyDescent="0.35">
       <c r="A37" s="2">
         <v>36</v>
       </c>
@@ -3299,7 +3321,7 @@
         <v>284</v>
       </c>
     </row>
-    <row r="38" spans="1:5" x14ac:dyDescent="0.25">
+    <row r="38" spans="1:5" x14ac:dyDescent="0.35">
       <c r="A38" s="2">
         <v>37</v>
       </c>
@@ -3316,7 +3338,7 @@
         <v>284</v>
       </c>
     </row>
-    <row r="39" spans="1:5" x14ac:dyDescent="0.25">
+    <row r="39" spans="1:5" x14ac:dyDescent="0.35">
       <c r="A39" s="2">
         <v>38</v>
       </c>
@@ -3333,7 +3355,7 @@
         <v>284</v>
       </c>
     </row>
-    <row r="40" spans="1:5" x14ac:dyDescent="0.25">
+    <row r="40" spans="1:5" x14ac:dyDescent="0.35">
       <c r="A40" s="2">
         <v>39</v>
       </c>
@@ -3350,7 +3372,7 @@
         <v>284</v>
       </c>
     </row>
-    <row r="41" spans="1:5" x14ac:dyDescent="0.25">
+    <row r="41" spans="1:5" x14ac:dyDescent="0.35">
       <c r="A41" s="2">
         <v>40</v>
       </c>
@@ -3367,7 +3389,7 @@
         <v>284</v>
       </c>
     </row>
-    <row r="42" spans="1:5" x14ac:dyDescent="0.25">
+    <row r="42" spans="1:5" x14ac:dyDescent="0.35">
       <c r="A42" s="2">
         <v>41</v>
       </c>
@@ -3384,7 +3406,7 @@
         <v>284</v>
       </c>
     </row>
-    <row r="43" spans="1:5" x14ac:dyDescent="0.25">
+    <row r="43" spans="1:5" x14ac:dyDescent="0.35">
       <c r="A43" s="2">
         <v>42</v>
       </c>
@@ -3401,7 +3423,7 @@
         <v>284</v>
       </c>
     </row>
-    <row r="44" spans="1:5" x14ac:dyDescent="0.25">
+    <row r="44" spans="1:5" x14ac:dyDescent="0.35">
       <c r="A44" s="2">
         <v>43</v>
       </c>
@@ -3418,7 +3440,7 @@
         <v>284</v>
       </c>
     </row>
-    <row r="45" spans="1:5" ht="26.25" x14ac:dyDescent="0.25">
+    <row r="45" spans="1:5" ht="26.5" x14ac:dyDescent="0.35">
       <c r="A45" s="2">
         <v>44</v>
       </c>
@@ -3435,7 +3457,7 @@
         <v>284</v>
       </c>
     </row>
-    <row r="46" spans="1:5" x14ac:dyDescent="0.25">
+    <row r="46" spans="1:5" x14ac:dyDescent="0.35">
       <c r="A46" s="2">
         <v>45</v>
       </c>
@@ -3452,7 +3474,7 @@
         <v>284</v>
       </c>
     </row>
-    <row r="47" spans="1:5" x14ac:dyDescent="0.25">
+    <row r="47" spans="1:5" x14ac:dyDescent="0.35">
       <c r="A47" s="2">
         <v>46</v>
       </c>
@@ -3469,7 +3491,7 @@
         <v>284</v>
       </c>
     </row>
-    <row r="48" spans="1:5" x14ac:dyDescent="0.25">
+    <row r="48" spans="1:5" x14ac:dyDescent="0.35">
       <c r="A48" s="2">
         <v>47</v>
       </c>
@@ -3486,7 +3508,7 @@
         <v>284</v>
       </c>
     </row>
-    <row r="49" spans="1:5" x14ac:dyDescent="0.25">
+    <row r="49" spans="1:5" x14ac:dyDescent="0.35">
       <c r="A49" s="2">
         <v>48</v>
       </c>
@@ -3503,7 +3525,7 @@
         <v>284</v>
       </c>
     </row>
-    <row r="50" spans="1:5" x14ac:dyDescent="0.25">
+    <row r="50" spans="1:5" x14ac:dyDescent="0.35">
       <c r="A50" s="2">
         <v>49</v>
       </c>
@@ -3520,7 +3542,7 @@
         <v>284</v>
       </c>
     </row>
-    <row r="51" spans="1:5" x14ac:dyDescent="0.25">
+    <row r="51" spans="1:5" x14ac:dyDescent="0.35">
       <c r="A51" s="2">
         <v>50</v>
       </c>
@@ -3537,7 +3559,7 @@
         <v>284</v>
       </c>
     </row>
-    <row r="52" spans="1:5" x14ac:dyDescent="0.25">
+    <row r="52" spans="1:5" x14ac:dyDescent="0.35">
       <c r="A52" s="2">
         <v>51</v>
       </c>
@@ -3554,7 +3576,7 @@
         <v>284</v>
       </c>
     </row>
-    <row r="53" spans="1:5" x14ac:dyDescent="0.25">
+    <row r="53" spans="1:5" x14ac:dyDescent="0.35">
       <c r="A53" s="2">
         <v>52</v>
       </c>
@@ -3571,7 +3593,7 @@
         <v>284</v>
       </c>
     </row>
-    <row r="54" spans="1:5" x14ac:dyDescent="0.25">
+    <row r="54" spans="1:5" x14ac:dyDescent="0.35">
       <c r="A54" s="2">
         <v>53</v>
       </c>
@@ -3588,7 +3610,7 @@
         <v>284</v>
       </c>
     </row>
-    <row r="55" spans="1:5" x14ac:dyDescent="0.25">
+    <row r="55" spans="1:5" x14ac:dyDescent="0.35">
       <c r="A55" s="2">
         <v>54</v>
       </c>
@@ -3605,7 +3627,7 @@
         <v>284</v>
       </c>
     </row>
-    <row r="56" spans="1:5" x14ac:dyDescent="0.25">
+    <row r="56" spans="1:5" x14ac:dyDescent="0.35">
       <c r="A56" s="2">
         <v>55</v>
       </c>
@@ -3622,7 +3644,7 @@
         <v>284</v>
       </c>
     </row>
-    <row r="57" spans="1:5" x14ac:dyDescent="0.25">
+    <row r="57" spans="1:5" x14ac:dyDescent="0.35">
       <c r="A57" s="2">
         <v>56</v>
       </c>
@@ -3639,7 +3661,7 @@
         <v>284</v>
       </c>
     </row>
-    <row r="58" spans="1:5" x14ac:dyDescent="0.25">
+    <row r="58" spans="1:5" x14ac:dyDescent="0.35">
       <c r="A58" s="2">
         <v>57</v>
       </c>
@@ -3656,7 +3678,7 @@
         <v>284</v>
       </c>
     </row>
-    <row r="59" spans="1:5" x14ac:dyDescent="0.25">
+    <row r="59" spans="1:5" x14ac:dyDescent="0.35">
       <c r="A59" s="2">
         <v>58</v>
       </c>
@@ -3673,7 +3695,7 @@
         <v>284</v>
       </c>
     </row>
-    <row r="60" spans="1:5" x14ac:dyDescent="0.25">
+    <row r="60" spans="1:5" x14ac:dyDescent="0.35">
       <c r="A60" s="2">
         <v>59</v>
       </c>
@@ -3690,7 +3712,7 @@
         <v>284</v>
       </c>
     </row>
-    <row r="61" spans="1:5" x14ac:dyDescent="0.25">
+    <row r="61" spans="1:5" x14ac:dyDescent="0.35">
       <c r="A61" s="2">
         <v>60</v>
       </c>
@@ -3707,7 +3729,7 @@
         <v>284</v>
       </c>
     </row>
-    <row r="62" spans="1:5" x14ac:dyDescent="0.25">
+    <row r="62" spans="1:5" x14ac:dyDescent="0.35">
       <c r="A62" s="2">
         <v>61</v>
       </c>
@@ -3724,7 +3746,7 @@
         <v>284</v>
       </c>
     </row>
-    <row r="63" spans="1:5" x14ac:dyDescent="0.25">
+    <row r="63" spans="1:5" x14ac:dyDescent="0.35">
       <c r="A63" s="2">
         <v>62</v>
       </c>
@@ -3741,7 +3763,7 @@
         <v>284</v>
       </c>
     </row>
-    <row r="64" spans="1:5" x14ac:dyDescent="0.25">
+    <row r="64" spans="1:5" x14ac:dyDescent="0.35">
       <c r="A64" s="2">
         <v>63</v>
       </c>
@@ -3758,7 +3780,7 @@
         <v>284</v>
       </c>
     </row>
-    <row r="65" spans="1:5" x14ac:dyDescent="0.25">
+    <row r="65" spans="1:5" x14ac:dyDescent="0.35">
       <c r="A65" s="4">
         <v>64</v>
       </c>
@@ -3775,7 +3797,7 @@
         <v>284</v>
       </c>
     </row>
-    <row r="66" spans="1:5" x14ac:dyDescent="0.25">
+    <row r="66" spans="1:5" x14ac:dyDescent="0.35">
       <c r="A66" s="2">
         <v>65</v>
       </c>
@@ -3792,7 +3814,7 @@
         <v>284</v>
       </c>
     </row>
-    <row r="67" spans="1:5" x14ac:dyDescent="0.25">
+    <row r="67" spans="1:5" x14ac:dyDescent="0.35">
       <c r="A67" s="2">
         <v>66</v>
       </c>
@@ -3809,7 +3831,7 @@
         <v>284</v>
       </c>
     </row>
-    <row r="68" spans="1:5" x14ac:dyDescent="0.25">
+    <row r="68" spans="1:5" x14ac:dyDescent="0.35">
       <c r="A68" s="2">
         <v>67</v>
       </c>
@@ -3826,7 +3848,7 @@
         <v>284</v>
       </c>
     </row>
-    <row r="69" spans="1:5" x14ac:dyDescent="0.25">
+    <row r="69" spans="1:5" x14ac:dyDescent="0.35">
       <c r="A69" s="2">
         <v>68</v>
       </c>
@@ -3843,7 +3865,7 @@
         <v>284</v>
       </c>
     </row>
-    <row r="70" spans="1:5" x14ac:dyDescent="0.25">
+    <row r="70" spans="1:5" x14ac:dyDescent="0.35">
       <c r="A70" s="2">
         <v>69</v>
       </c>
@@ -3860,7 +3882,7 @@
         <v>284</v>
       </c>
     </row>
-    <row r="71" spans="1:5" ht="26.25" x14ac:dyDescent="0.25">
+    <row r="71" spans="1:5" x14ac:dyDescent="0.35">
       <c r="A71" s="2">
         <v>70</v>
       </c>
@@ -3877,7 +3899,7 @@
         <v>284</v>
       </c>
     </row>
-    <row r="72" spans="1:5" x14ac:dyDescent="0.25">
+    <row r="72" spans="1:5" x14ac:dyDescent="0.35">
       <c r="A72" s="2">
         <v>71</v>
       </c>
@@ -3894,7 +3916,7 @@
         <v>284</v>
       </c>
     </row>
-    <row r="73" spans="1:5" x14ac:dyDescent="0.25">
+    <row r="73" spans="1:5" x14ac:dyDescent="0.35">
       <c r="A73" s="2">
         <v>72</v>
       </c>
@@ -3911,7 +3933,7 @@
         <v>284</v>
       </c>
     </row>
-    <row r="74" spans="1:5" x14ac:dyDescent="0.25">
+    <row r="74" spans="1:5" x14ac:dyDescent="0.35">
       <c r="A74" s="2">
         <v>73</v>
       </c>
@@ -3928,7 +3950,7 @@
         <v>284</v>
       </c>
     </row>
-    <row r="75" spans="1:5" x14ac:dyDescent="0.25">
+    <row r="75" spans="1:5" x14ac:dyDescent="0.35">
       <c r="A75" s="2">
         <v>74</v>
       </c>
@@ -3945,7 +3967,7 @@
         <v>284</v>
       </c>
     </row>
-    <row r="76" spans="1:5" x14ac:dyDescent="0.25">
+    <row r="76" spans="1:5" x14ac:dyDescent="0.35">
       <c r="A76" s="2">
         <v>75</v>
       </c>
@@ -3962,7 +3984,7 @@
         <v>284</v>
       </c>
     </row>
-    <row r="77" spans="1:5" ht="26.25" x14ac:dyDescent="0.25">
+    <row r="77" spans="1:5" x14ac:dyDescent="0.35">
       <c r="A77" s="2">
         <v>76</v>
       </c>
@@ -3979,7 +4001,7 @@
         <v>284</v>
       </c>
     </row>
-    <row r="78" spans="1:5" x14ac:dyDescent="0.25">
+    <row r="78" spans="1:5" x14ac:dyDescent="0.35">
       <c r="A78" s="2">
         <v>77</v>
       </c>
@@ -3996,7 +4018,7 @@
         <v>284</v>
       </c>
     </row>
-    <row r="79" spans="1:5" x14ac:dyDescent="0.25">
+    <row r="79" spans="1:5" x14ac:dyDescent="0.35">
       <c r="A79" s="2">
         <v>78</v>
       </c>
@@ -4013,7 +4035,7 @@
         <v>284</v>
       </c>
     </row>
-    <row r="80" spans="1:5" ht="26.25" x14ac:dyDescent="0.25">
+    <row r="80" spans="1:5" ht="26.5" x14ac:dyDescent="0.35">
       <c r="A80" s="2">
         <v>79</v>
       </c>
@@ -4030,7 +4052,7 @@
         <v>284</v>
       </c>
     </row>
-    <row r="81" spans="1:5" x14ac:dyDescent="0.25">
+    <row r="81" spans="1:5" x14ac:dyDescent="0.35">
       <c r="A81" s="2">
         <v>80</v>
       </c>
@@ -4047,7 +4069,7 @@
         <v>284</v>
       </c>
     </row>
-    <row r="82" spans="1:5" x14ac:dyDescent="0.25">
+    <row r="82" spans="1:5" x14ac:dyDescent="0.35">
       <c r="A82" s="2">
         <v>81</v>
       </c>
@@ -4064,7 +4086,7 @@
         <v>284</v>
       </c>
     </row>
-    <row r="83" spans="1:5" x14ac:dyDescent="0.25">
+    <row r="83" spans="1:5" x14ac:dyDescent="0.35">
       <c r="A83" s="2">
         <v>82</v>
       </c>
@@ -4081,7 +4103,7 @@
         <v>284</v>
       </c>
     </row>
-    <row r="84" spans="1:5" x14ac:dyDescent="0.25">
+    <row r="84" spans="1:5" x14ac:dyDescent="0.35">
       <c r="A84" s="2">
         <v>83</v>
       </c>
@@ -4098,7 +4120,7 @@
         <v>284</v>
       </c>
     </row>
-    <row r="85" spans="1:5" x14ac:dyDescent="0.25">
+    <row r="85" spans="1:5" x14ac:dyDescent="0.35">
       <c r="A85" s="2">
         <v>84</v>
       </c>
@@ -4115,7 +4137,7 @@
         <v>284</v>
       </c>
     </row>
-    <row r="86" spans="1:5" x14ac:dyDescent="0.25">
+    <row r="86" spans="1:5" x14ac:dyDescent="0.35">
       <c r="A86" s="2">
         <v>85</v>
       </c>
@@ -4132,7 +4154,7 @@
         <v>284</v>
       </c>
     </row>
-    <row r="87" spans="1:5" x14ac:dyDescent="0.25">
+    <row r="87" spans="1:5" x14ac:dyDescent="0.35">
       <c r="A87" s="2">
         <v>86</v>
       </c>
@@ -4149,7 +4171,7 @@
         <v>284</v>
       </c>
     </row>
-    <row r="88" spans="1:5" x14ac:dyDescent="0.25">
+    <row r="88" spans="1:5" x14ac:dyDescent="0.35">
       <c r="A88" s="2">
         <v>87</v>
       </c>
@@ -4166,7 +4188,7 @@
         <v>284</v>
       </c>
     </row>
-    <row r="89" spans="1:5" x14ac:dyDescent="0.25">
+    <row r="89" spans="1:5" x14ac:dyDescent="0.35">
       <c r="A89" s="2">
         <v>88</v>
       </c>
@@ -4183,7 +4205,7 @@
         <v>284</v>
       </c>
     </row>
-    <row r="90" spans="1:5" x14ac:dyDescent="0.25">
+    <row r="90" spans="1:5" x14ac:dyDescent="0.35">
       <c r="A90" s="2">
         <v>89</v>
       </c>
@@ -4200,7 +4222,7 @@
         <v>284</v>
       </c>
     </row>
-    <row r="91" spans="1:5" ht="26.25" x14ac:dyDescent="0.25">
+    <row r="91" spans="1:5" ht="26.5" x14ac:dyDescent="0.35">
       <c r="A91" s="2">
         <v>90</v>
       </c>
@@ -4217,7 +4239,7 @@
         <v>284</v>
       </c>
     </row>
-    <row r="92" spans="1:5" x14ac:dyDescent="0.25">
+    <row r="92" spans="1:5" x14ac:dyDescent="0.35">
       <c r="A92" s="2">
         <v>91</v>
       </c>
@@ -4234,7 +4256,7 @@
         <v>284</v>
       </c>
     </row>
-    <row r="93" spans="1:5" x14ac:dyDescent="0.25">
+    <row r="93" spans="1:5" x14ac:dyDescent="0.35">
       <c r="A93" s="2">
         <v>92</v>
       </c>
@@ -4251,7 +4273,7 @@
         <v>284</v>
       </c>
     </row>
-    <row r="94" spans="1:5" x14ac:dyDescent="0.25">
+    <row r="94" spans="1:5" x14ac:dyDescent="0.35">
       <c r="A94" s="2">
         <v>93</v>
       </c>
@@ -4268,7 +4290,7 @@
         <v>284</v>
       </c>
     </row>
-    <row r="95" spans="1:5" x14ac:dyDescent="0.25">
+    <row r="95" spans="1:5" x14ac:dyDescent="0.35">
       <c r="A95" s="2">
         <v>94</v>
       </c>
@@ -4285,7 +4307,7 @@
         <v>284</v>
       </c>
     </row>
-    <row r="96" spans="1:5" x14ac:dyDescent="0.25">
+    <row r="96" spans="1:5" x14ac:dyDescent="0.35">
       <c r="A96" s="2">
         <v>95</v>
       </c>
@@ -4302,7 +4324,7 @@
         <v>284</v>
       </c>
     </row>
-    <row r="97" spans="1:5" x14ac:dyDescent="0.25">
+    <row r="97" spans="1:5" x14ac:dyDescent="0.35">
       <c r="A97" s="2">
         <v>96</v>
       </c>
@@ -4325,17 +4347,17 @@
       <sortCondition ref="B1:B33"/>
     </sortState>
   </autoFilter>
-  <conditionalFormatting sqref="B24:B25">
-    <cfRule type="duplicateValues" dxfId="5" priority="5"/>
-  </conditionalFormatting>
   <conditionalFormatting sqref="B22">
     <cfRule type="duplicateValues" dxfId="4" priority="4"/>
   </conditionalFormatting>
+  <conditionalFormatting sqref="B24:B25">
+    <cfRule type="duplicateValues" dxfId="3" priority="5"/>
+  </conditionalFormatting>
   <conditionalFormatting sqref="B32">
-    <cfRule type="duplicateValues" dxfId="3" priority="3"/>
+    <cfRule type="duplicateValues" dxfId="2" priority="3"/>
   </conditionalFormatting>
   <conditionalFormatting sqref="B96">
-    <cfRule type="duplicateValues" dxfId="2" priority="2"/>
+    <cfRule type="duplicateValues" dxfId="1" priority="2"/>
   </conditionalFormatting>
   <conditionalFormatting sqref="B97">
     <cfRule type="duplicateValues" dxfId="0" priority="1"/>
